--- a/database.xlsx
+++ b/database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Desktop\Crop_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BF36C6D-11ED-4C1A-928B-6381C0FB1E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DDBF064-27EE-4AE7-B593-A4AA87C0A215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="794">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1138" uniqueCount="838">
   <si>
     <t>Oryza Sativa</t>
   </si>
@@ -8694,6 +8694,138 @@
   </si>
   <si>
     <t>coconut.jpg</t>
+  </si>
+  <si>
+    <t>80 - 175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 - 60 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">120 - 150 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 - 80 </t>
+  </si>
+  <si>
+    <t>40 - 60</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 - 120 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 - 50 </t>
+  </si>
+  <si>
+    <t>60 - 100</t>
+  </si>
+  <si>
+    <t>30 - 50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 - 50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 - 40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">20 - 30 </t>
+  </si>
+  <si>
+    <t>120 - 180</t>
+  </si>
+  <si>
+    <t>60 - 75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 - 75 </t>
+  </si>
+  <si>
+    <t>150 - 300</t>
+  </si>
+  <si>
+    <t>60 - 125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">100 - 150 </t>
+  </si>
+  <si>
+    <t>40 - 150</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 - 40 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">30 - 60 </t>
+  </si>
+  <si>
+    <t>60 - 80</t>
+  </si>
+  <si>
+    <t>17 - 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34 - 60 </t>
+  </si>
+  <si>
+    <t>25 - 54</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40 - 60 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 - 120 </t>
+  </si>
+  <si>
+    <t>40 - 80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50 - 90 </t>
+  </si>
+  <si>
+    <t>40 - 100</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 - 50 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">150 - 250 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 - 120 </t>
+  </si>
+  <si>
+    <t>80 - 140</t>
+  </si>
+  <si>
+    <t xml:space="preserve">60 - 100 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">80 - 140 </t>
+  </si>
+  <si>
+    <t>30 - 90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45 - 100 </t>
+  </si>
+  <si>
+    <t>26 - 152</t>
+  </si>
+  <si>
+    <t>80 - 100</t>
+  </si>
+  <si>
+    <t>175 - 210</t>
+  </si>
+  <si>
+    <t>n_range</t>
+  </si>
+  <si>
+    <t>p_range</t>
+  </si>
+  <si>
+    <t>k_range</t>
   </si>
 </sst>
 </file>
@@ -9483,7 +9615,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="17" customWidth="1"/>
@@ -9493,7 +9625,7 @@
     <col min="6" max="6" width="14.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>182</v>
       </c>
@@ -9512,8 +9644,17 @@
       <c r="F1" s="35" t="s">
         <v>775</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G1" s="35" t="s">
+        <v>835</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>836</v>
+      </c>
+      <c r="I1" s="35" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -9532,8 +9673,17 @@
       <c r="F2" s="3" t="s">
         <v>776</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G2" s="3" t="s">
+        <v>794</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>795</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -9552,8 +9702,17 @@
       <c r="F3" s="3" t="s">
         <v>777</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G3" s="3" t="s">
+        <v>796</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>797</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>798</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -9572,8 +9731,17 @@
       <c r="F4" s="3" t="s">
         <v>778</v>
       </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G4" s="15" t="s">
+        <v>799</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="I4" s="15" t="s">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -9592,8 +9760,17 @@
       <c r="F5" s="3" t="s">
         <v>779</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G5" s="15" t="s">
+        <v>801</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>802</v>
+      </c>
+      <c r="I5" s="15" t="s">
+        <v>803</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -9612,8 +9789,17 @@
       <c r="F6" s="3" t="s">
         <v>780</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G6" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="H6" s="15" t="s">
+        <v>804</v>
+      </c>
+      <c r="I6" s="15" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -9632,8 +9818,17 @@
       <c r="F7" s="3" t="s">
         <v>781</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G7" s="15" t="s">
+        <v>806</v>
+      </c>
+      <c r="H7" s="15" t="s">
+        <v>807</v>
+      </c>
+      <c r="I7" s="15" t="s">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -9652,8 +9847,17 @@
       <c r="F8" s="3" t="s">
         <v>782</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G8" s="15" t="s">
+        <v>809</v>
+      </c>
+      <c r="H8" s="15" t="s">
+        <v>810</v>
+      </c>
+      <c r="I8" s="15" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -9672,8 +9876,17 @@
       <c r="F9" s="3" t="s">
         <v>783</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G9" s="15" t="s">
+        <v>812</v>
+      </c>
+      <c r="H9" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="I9" s="15" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -9692,8 +9905,17 @@
       <c r="F10" s="3" t="s">
         <v>784</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G10" s="15" t="s">
+        <v>815</v>
+      </c>
+      <c r="H10" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="I10" s="15" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -9712,8 +9934,17 @@
       <c r="F11" s="3" t="s">
         <v>785</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G11" s="15" t="s">
+        <v>816</v>
+      </c>
+      <c r="H11" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="I11" s="15" t="s">
+        <v>818</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -9732,8 +9963,17 @@
       <c r="F12" s="3" t="s">
         <v>786</v>
       </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G12" s="15" t="s">
+        <v>820</v>
+      </c>
+      <c r="H12" s="15" t="s">
+        <v>819</v>
+      </c>
+      <c r="I12" s="15" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -9752,8 +9992,17 @@
       <c r="F13" s="3" t="s">
         <v>787</v>
       </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G13" s="15" t="s">
+        <v>805</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>797</v>
+      </c>
+      <c r="I13" s="15" t="s">
+        <v>804</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -9772,8 +10021,17 @@
       <c r="F14" s="3" t="s">
         <v>788</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G14" s="15" t="s">
+        <v>821</v>
+      </c>
+      <c r="H14" s="15" t="s">
+        <v>822</v>
+      </c>
+      <c r="I14" s="15" t="s">
+        <v>819</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -9792,8 +10050,17 @@
       <c r="F15" s="3" t="s">
         <v>789</v>
       </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G15" s="15" t="s">
+        <v>823</v>
+      </c>
+      <c r="H15" s="15" t="s">
+        <v>824</v>
+      </c>
+      <c r="I15" s="15" t="s">
+        <v>824</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
@@ -9812,8 +10079,17 @@
       <c r="F16" s="3" t="s">
         <v>790</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G16" s="15" t="s">
+        <v>825</v>
+      </c>
+      <c r="H16" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>826</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
         <v>16</v>
       </c>
@@ -9832,8 +10108,17 @@
       <c r="F17" s="3" t="s">
         <v>791</v>
       </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G17" s="15" t="s">
+        <v>827</v>
+      </c>
+      <c r="H17" s="15" t="s">
+        <v>828</v>
+      </c>
+      <c r="I17" s="15" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
         <v>17</v>
       </c>
@@ -9852,8 +10137,17 @@
       <c r="F18" s="3" t="s">
         <v>792</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G18" s="15" t="s">
+        <v>830</v>
+      </c>
+      <c r="H18" s="15" t="s">
+        <v>831</v>
+      </c>
+      <c r="I18" s="15" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
         <v>18</v>
       </c>
@@ -9872,8 +10166,17 @@
       <c r="F19" s="3" t="s">
         <v>793</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="G19" s="15" t="s">
+        <v>833</v>
+      </c>
+      <c r="H19" s="15" t="s">
+        <v>795</v>
+      </c>
+      <c r="I19" s="15" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
     </row>
   </sheetData>
@@ -9884,14 +10187,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51FBC92F-F859-4168-955B-F4300B2BF9D1}">
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="45.85546875" customWidth="1"/>
     <col min="4" max="4" width="18.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" customWidth="1"/>
+    <col min="7" max="7" width="14.140625" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>187</v>
       </c>
@@ -9907,8 +10213,11 @@
       <c r="E1" s="2" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="35"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
         <v>1</v>
       </c>
@@ -9925,7 +10234,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
         <v>2</v>
       </c>
@@ -9942,7 +10251,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
         <v>3</v>
       </c>
@@ -9959,7 +10268,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
         <v>4</v>
       </c>
@@ -9976,7 +10285,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
         <v>5</v>
       </c>
@@ -9993,7 +10302,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
         <v>6</v>
       </c>
@@ -10010,7 +10319,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
         <v>7</v>
       </c>
@@ -10027,7 +10336,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
         <v>8</v>
       </c>
@@ -10044,7 +10353,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
         <v>9</v>
       </c>
@@ -10061,7 +10370,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
         <v>10</v>
       </c>
@@ -10078,7 +10387,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
         <v>11</v>
       </c>
@@ -10095,7 +10404,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
         <v>12</v>
       </c>
@@ -10112,7 +10421,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="14" spans="1:5" ht="60" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:8" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
         <v>13</v>
       </c>
@@ -10129,7 +10438,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="15" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
         <v>14</v>
       </c>
@@ -10146,7 +10455,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
         <v>15</v>
       </c>
